--- a/consent_forms/039_firearms_training_release_form--consent_forms.xlsx
+++ b/consent_forms/039_firearms_training_release_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i_will_not_touch_any_live_fire_until_i_have_been_properly_cleared_by_an_instructor.</t>
+          <t>i_will_keep_my_finger_off_the_trigger_until_i_am_ready_to_shoot.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I will not touch any live fire until I have been properly cleared by an instructor.</t>
+          <t>I will keep my finger off the trigger until I am ready to shoot.</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>i_will_keep_my_finger_off_the_trigger_until_i_am_ready_to_shoot.</t>
+          <t>i_will_be_aware_of_my_surroundings.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I will keep my finger off the trigger until I am ready to shoot.</t>
+          <t>I will be aware of my surroundings.</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i_will_be_aware_of_my_surroundings.</t>
+          <t>i_will_follow_all_safety_rules.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I will be aware of my surroundings.</t>
+          <t>I will follow all safety rules.</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i_will_follow_all_safety_rules.</t>
+          <t>i_will_keep_a_safe_distance_from_other_students.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I will follow all safety rules.</t>
+          <t>I will keep a safe distance from other students.</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i_will_keep_a_safe_distance_from_other_students.</t>
+          <t>i_will_follow_all_instructions_given_by_the_instructor.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I will keep a safe distance from other students.</t>
+          <t>I will follow all instructions given by the instructor.</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i_will_follow_all_instructions_given_by_the_instructor.</t>
+          <t>i_will_wear_eye_and_ear_protection_at_all_times.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>I will follow all instructions given by the instructor.</t>
+          <t>I will wear eye and ear protection at all times.</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>i_will_wear_eye_and_ear_protection_at_all_times.</t>
+          <t>i_will_keep_my_hands_and_face_covered_during_all_live_fire_exercises.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I will wear eye and ear protection at all times.</t>
+          <t>I will keep my hands and face covered during all live fire exercises.</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>i_will_keep_my_hands_and_face_covered_during_all_live_fire_exercises.</t>
+          <t>i_will_stay_alert_and_awake_during_all_training_sessions.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>I will keep my hands and face covered during all live fire exercises.</t>
+          <t>I will stay alert and awake during all training sessions.</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i_will_follow_all_safety_rules.</t>
+          <t>i_will_not_shoot_at_any_object_that_is_not_authorized_by_the_instructor.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>I will follow all safety rules.</t>
+          <t>I will not shoot at any object that is not authorized by the instructor.</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i_will_stay_alert_and_awake_during_all_training_sessions.</t>
+          <t>i_will_not_take_any_live_fire_until_i_have_been_properly_cleared_by_an_instructor.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>I will stay alert and awake during all training sessions.</t>
+          <t>I will not take any live fire until I have been properly cleared by an instructor.</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i_will_not_shoot_at_any_object_that_is_not_authorized_by_the_instructor.</t>
+          <t>i_will_keep_my_face_and_hair_covered_during_all_live_fire_exercises.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I will not shoot at any object that is not authorized by the instructor.</t>
+          <t>I will keep my face and hair covered during all live fire exercises.</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i_will_not_take_any_live_fire_until_i_have_been_properly_cleared_by_an_instructor.</t>
+          <t>i_will_be_aware_of_my_surroundings_at_all_times.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>I will not take any live fire until I have been properly cleared by an instructor.</t>
+          <t>I will be aware of my surroundings at all times.</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i_will_follow_all_safety_rules.</t>
+          <t>i_will_not_touch_or_manipulate_any_live_fire_until_i_have_been_properly_cleared_by_an_instructor.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>I will follow all safety rules.</t>
+          <t>I will not touch or manipulate any live fire until I have been properly cleared by an instructor.</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i_will_keep_my_face_and_hair_covered_during_all_live_fire_exercises.</t>
+          <t>i_will_not_take_any_unauthorized_live_fire.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>I will keep my face and hair covered during all live fire exercises.</t>
+          <t>I will not take any unauthorized live fire.</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i_will_follow_all_rules_and_regulations.</t>
+          <t>i_will_wear_proper_safety_equipment_at_all_times.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>I will follow all rules and regulations.</t>
+          <t>I will wear proper safety equipment at all times.</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i_will_be_aware_of_my_surroundings_at_all_times.</t>
+          <t>i_will_be_aware_of_the_target.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>I will be aware of my surroundings at all times.</t>
+          <t>I will be aware of the target.</t>
         </is>
       </c>
     </row>
@@ -1496,80 +1496,80 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i_will_not_touch_or_manipulate_any_live_fire_until_i_have_been_properly_cleared_by_an_instructor.</t>
+          <t>i_will_not_shoot_at_the_instructor.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I will not touch or manipulate any live fire until I have been properly cleared by an instructor.</t>
+          <t>I will not shoot at the instructor.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>participant_agree_choices</t>
+          <t>instructor_agreement_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i_will_not_take_any_unauthorized_live_fire.</t>
+          <t>i_will_keep_a_safe_distance_from_students.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>I will not take any unauthorized live fire.</t>
+          <t>I will keep a safe distance from students.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>participant_agree_choices</t>
+          <t>instructor_agreement_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i_will_wear_proper_safety_equipment_at_all_times.</t>
+          <t>i_will_keep_all_safety_equipment_at_all_times.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I will wear proper safety equipment at all times.</t>
+          <t>I will keep all safety equipment at all times.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>participant_agree_choices</t>
+          <t>instructor_agreement_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i_will_be_aware_of_the_target.</t>
+          <t>i_will_make_sure_students_are_aware_of_their_surroundings.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>I will be aware of the target.</t>
+          <t>I will make sure students are aware of their surroundings.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>participant_agree_choices</t>
+          <t>instructor_agreement_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i_will_not_shoot_at_the_instructor.</t>
+          <t>i_will_follow_all_safety_rules.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>I will not shoot at the instructor.</t>
+          <t>I will follow all safety rules.</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i_will_keep_a_safe_distance_from_students.</t>
+          <t>i_will_not_touch_any_live_fire_until_i_have_been_properly_cleared_by_a_student.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>I will keep a safe distance from students.</t>
+          <t>I will not touch any live fire until I have been properly cleared by a student.</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i_will_keep_all_safety_equipment_at_all_times.</t>
+          <t>i_will_keep_students_informed_of_any_safety_rules.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>I will keep all safety equipment at all times.</t>
+          <t>I will keep students informed of any safety rules.</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>i_will_make_sure_students_are_aware_of_their_surroundings.</t>
+          <t>i_will_not_let_students_shoot_at_the_instructor.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>I will make sure students are aware of their surroundings.</t>
+          <t>I will not let students shoot at the instructor.</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>i_will_follow_all_safety_rules.</t>
+          <t>i_will_keep_a_safe_distance_from_other_instructors.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>I will follow all safety rules.</t>
+          <t>I will keep a safe distance from other instructors.</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>i_will_not_touch_any_live_fire_until_i_have_been_properly_cleared_by_a_student.</t>
+          <t>i_will_keep_a_safe_distance_from_other_students.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>I will not touch any live fire until I have been properly cleared by a student.</t>
+          <t>I will keep a safe distance from other students.</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i_will_keep_students_informed_of_any_safety_rules.</t>
+          <t>i_will_make_sure_students_are_aware_of_the_target.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>I will keep students informed of any safety rules.</t>
+          <t>I will make sure students are aware of the target.</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i_will_not_let_students_shoot_at_the_instructor.</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>I will not let students shoot at the instructor.</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1700,367 +1700,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i_will_keep_a_safe_distance_from_other_instructors.</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>I will keep a safe distance from other instructors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>i_will_keep_students_informed_of_any_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>I will keep students informed of any safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>i_will_keep_a_safe_distance_from_students.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>I will keep a safe distance from students.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>i_will_keep_a_safe_distance_from_other_students.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>I will keep a safe distance from other students.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>i_will_make_sure_students_are_aware_of_the_target.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>I will make sure students are aware of the target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>i_will_keep_students_informed_of_any_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>I will keep students informed of any safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>i_will_keep_a_safe_distance_from_students.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>I will keep a safe distance from students.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>i_will_make_sure_students_are_aware_of_their_surroundings.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>I will make sure students are aware of their surroundings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>i_will_keep_students_informed_of_any_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>I will keep students informed of any safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>i_will_keep_a_safe_distance_from_other_instructors.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>I will keep a safe distance from other instructors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>i_will_follow_all_safety_rules.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>I will follow all safety rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>i_agree</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>I agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>instructor_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>i_do_not_agree</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>I do not agree</t>
         </is>
